--- a/DataDriven_Framework/DataTables/TestData.xlsx
+++ b/DataDriven_Framework/DataTables/TestData.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Analogfotography\DataDriven_Framework\DataTables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7959699-66C7-40AD-93E5-4B80B078F650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9CF37596-7323-4D88-A8A1-18A621B6151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D86A5495-945F-4A9E-A9C5-E194C0262502}"/>
   </bookViews>
@@ -16,6 +11,7 @@
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:P13"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
